--- a/3. GHFM_Daily/Investment thesis/2025/202507/GHFM_InvestmentThesis_20250714.xlsx
+++ b/3. GHFM_Daily/Investment thesis/2025/202507/GHFM_InvestmentThesis_20250714.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29206"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GHFM\JY\Jing Yan_reporting backup\1. GHFM Reporting\3. GHFM_Daily\Investment thesis\202507\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://goldenhorsefm-my.sharepoint.com/personal/investments_ghfm_fund/Documents/Investments Team/GHFM-Daily-Portfolio-Reporting/3. GHFM_Daily/Investment thesis/2025/202507/"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54B1EB12-2BD8-4126-A546-9AFDD80FE930}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="17295" yWindow="-15045" windowWidth="33135" windowHeight="13710" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Market Value" sheetId="3" r:id="rId1"/>
@@ -419,7 +419,7 @@
     <numFmt numFmtId="168" formatCode="\$#,##0.00;\-\$#,##0.00"/>
     <numFmt numFmtId="169" formatCode="0.00_);[Red]\(0.00\)"/>
   </numFmts>
-  <fonts count="12">
+  <fonts count="12" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -4979,7 +4979,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:K224"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="13.9"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="36.85546875" style="9" customWidth="1"/>
     <col min="2" max="10" width="20.7109375" style="1" customWidth="1"/>
@@ -4988,7 +4988,7 @@
     <col min="14" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" customFormat="1" ht="14.45">
+    <row r="1" spans="1:11" customFormat="1" ht="15" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
         <v>0</v>
       </c>
@@ -4997,7 +4997,7 @@
       </c>
       <c r="K1" s="17"/>
     </row>
-    <row r="2" spans="1:11" customFormat="1" ht="14.45">
+    <row r="2" spans="1:11" customFormat="1" ht="15" x14ac:dyDescent="0.25">
       <c r="A2" s="7" t="s">
         <v>1</v>
       </c>
@@ -5006,7 +5006,7 @@
       </c>
       <c r="K2" s="17"/>
     </row>
-    <row r="3" spans="1:11" customFormat="1" ht="14.45">
+    <row r="3" spans="1:11" customFormat="1" ht="15" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
         <v>2</v>
       </c>
@@ -5016,7 +5016,7 @@
       </c>
       <c r="K3" s="17"/>
     </row>
-    <row r="4" spans="1:11" customFormat="1" ht="14.45">
+    <row r="4" spans="1:11" customFormat="1" ht="15" x14ac:dyDescent="0.25">
       <c r="A4" s="6" t="s">
         <v>3</v>
       </c>
@@ -5026,7 +5026,7 @@
       </c>
       <c r="K4" s="17"/>
     </row>
-    <row r="5" spans="1:11" customFormat="1" ht="14.45">
+    <row r="5" spans="1:11" customFormat="1" ht="15" x14ac:dyDescent="0.25">
       <c r="A5" s="6" t="s">
         <v>4</v>
       </c>
@@ -5036,7 +5036,7 @@
       </c>
       <c r="K5" s="17"/>
     </row>
-    <row r="6" spans="1:11" customFormat="1" ht="14.45">
+    <row r="6" spans="1:11" customFormat="1" ht="15" x14ac:dyDescent="0.25">
       <c r="A6" s="6" t="s">
         <v>5</v>
       </c>
@@ -5046,7 +5046,7 @@
       </c>
       <c r="K6" s="17"/>
     </row>
-    <row r="7" spans="1:11" customFormat="1" ht="14.45">
+    <row r="7" spans="1:11" customFormat="1" ht="15" x14ac:dyDescent="0.25">
       <c r="A7" s="6" t="s">
         <v>6</v>
       </c>
@@ -5056,7 +5056,7 @@
       </c>
       <c r="K7" s="17"/>
     </row>
-    <row r="8" spans="1:11" customFormat="1" ht="14.45">
+    <row r="8" spans="1:11" customFormat="1" ht="15" x14ac:dyDescent="0.25">
       <c r="A8" s="6" t="s">
         <v>7</v>
       </c>
@@ -5066,7 +5066,7 @@
       </c>
       <c r="K8" s="17"/>
     </row>
-    <row r="9" spans="1:11" customFormat="1" ht="14.45">
+    <row r="9" spans="1:11" customFormat="1" ht="15" x14ac:dyDescent="0.25">
       <c r="A9" s="6" t="s">
         <v>8</v>
       </c>
@@ -5076,7 +5076,7 @@
       </c>
       <c r="K9" s="17"/>
     </row>
-    <row r="10" spans="1:11" customFormat="1" ht="14.45">
+    <row r="10" spans="1:11" customFormat="1" ht="15" x14ac:dyDescent="0.25">
       <c r="A10" s="6" t="s">
         <v>9</v>
       </c>
@@ -5086,7 +5086,7 @@
       </c>
       <c r="K10" s="17"/>
     </row>
-    <row r="11" spans="1:11" customFormat="1" ht="14.45">
+    <row r="11" spans="1:11" customFormat="1" ht="15" x14ac:dyDescent="0.25">
       <c r="A11" s="6" t="s">
         <v>10</v>
       </c>
@@ -5096,7 +5096,7 @@
       </c>
       <c r="K11" s="17"/>
     </row>
-    <row r="12" spans="1:11" customFormat="1" ht="14.45">
+    <row r="12" spans="1:11" customFormat="1" ht="15" x14ac:dyDescent="0.25">
       <c r="A12" s="6" t="s">
         <v>11</v>
       </c>
@@ -5106,7 +5106,7 @@
       </c>
       <c r="K12" s="17"/>
     </row>
-    <row r="13" spans="1:11" customFormat="1" ht="14.45">
+    <row r="13" spans="1:11" customFormat="1" ht="15" x14ac:dyDescent="0.25">
       <c r="A13" s="6" t="s">
         <v>12</v>
       </c>
@@ -5116,7 +5116,7 @@
       </c>
       <c r="K13" s="17"/>
     </row>
-    <row r="14" spans="1:11" customFormat="1" ht="14.45">
+    <row r="14" spans="1:11" customFormat="1" ht="15" x14ac:dyDescent="0.25">
       <c r="A14" s="6" t="s">
         <v>13</v>
       </c>
@@ -5126,7 +5126,7 @@
       </c>
       <c r="K14" s="17"/>
     </row>
-    <row r="15" spans="1:11" customFormat="1" ht="14.45">
+    <row r="15" spans="1:11" customFormat="1" ht="15" x14ac:dyDescent="0.25">
       <c r="A15" s="6" t="s">
         <v>14</v>
       </c>
@@ -5136,7 +5136,7 @@
       </c>
       <c r="K15" s="17"/>
     </row>
-    <row r="16" spans="1:11" customFormat="1" ht="14.45">
+    <row r="16" spans="1:11" customFormat="1" ht="15" x14ac:dyDescent="0.25">
       <c r="A16" s="6" t="s">
         <v>15</v>
       </c>
@@ -5146,7 +5146,7 @@
       </c>
       <c r="K16" s="17"/>
     </row>
-    <row r="17" spans="1:11" customFormat="1" ht="14.45">
+    <row r="17" spans="1:11" customFormat="1" ht="15" x14ac:dyDescent="0.25">
       <c r="A17" s="6" t="s">
         <v>16</v>
       </c>
@@ -5156,7 +5156,7 @@
       </c>
       <c r="K17" s="17"/>
     </row>
-    <row r="18" spans="1:11" customFormat="1" ht="14.45">
+    <row r="18" spans="1:11" customFormat="1" ht="15" x14ac:dyDescent="0.25">
       <c r="A18" s="6" t="s">
         <v>17</v>
       </c>
@@ -5166,7 +5166,7 @@
       </c>
       <c r="K18" s="17"/>
     </row>
-    <row r="19" spans="1:11" customFormat="1" ht="14.45">
+    <row r="19" spans="1:11" customFormat="1" ht="15" x14ac:dyDescent="0.25">
       <c r="A19" s="6" t="s">
         <v>18</v>
       </c>
@@ -5176,7 +5176,7 @@
       </c>
       <c r="K19" s="17"/>
     </row>
-    <row r="20" spans="1:11" customFormat="1" ht="14.45">
+    <row r="20" spans="1:11" customFormat="1" ht="15" x14ac:dyDescent="0.25">
       <c r="A20" s="8" t="s">
         <v>19</v>
       </c>
@@ -5186,7 +5186,7 @@
       </c>
       <c r="K20" s="17"/>
     </row>
-    <row r="21" spans="1:11" customFormat="1" ht="14.45">
+    <row r="21" spans="1:11" customFormat="1" ht="15" x14ac:dyDescent="0.25">
       <c r="A21" s="6" t="s">
         <v>20</v>
       </c>
@@ -5196,7 +5196,7 @@
       </c>
       <c r="K21" s="17"/>
     </row>
-    <row r="22" spans="1:11" customFormat="1" ht="14.45">
+    <row r="22" spans="1:11" customFormat="1" ht="15" x14ac:dyDescent="0.25">
       <c r="A22" s="7" t="s">
         <v>21</v>
       </c>
@@ -5205,7 +5205,7 @@
       </c>
       <c r="K22" s="17"/>
     </row>
-    <row r="23" spans="1:11" customFormat="1" ht="14.45">
+    <row r="23" spans="1:11" customFormat="1" ht="15" x14ac:dyDescent="0.25">
       <c r="A23" s="7" t="s">
         <v>22</v>
       </c>
@@ -5214,7 +5214,7 @@
       </c>
       <c r="K23" s="17"/>
     </row>
-    <row r="24" spans="1:11" customFormat="1" ht="14.45">
+    <row r="24" spans="1:11" customFormat="1" ht="15" x14ac:dyDescent="0.25">
       <c r="A24" s="7" t="s">
         <v>23</v>
       </c>
@@ -5223,7 +5223,7 @@
       </c>
       <c r="K24" s="17"/>
     </row>
-    <row r="25" spans="1:11" customFormat="1" ht="14.45">
+    <row r="25" spans="1:11" customFormat="1" ht="15" x14ac:dyDescent="0.25">
       <c r="A25" s="7" t="s">
         <v>24</v>
       </c>
@@ -5233,7 +5233,7 @@
       </c>
       <c r="K25" s="17"/>
     </row>
-    <row r="26" spans="1:11" customFormat="1" ht="27.75" customHeight="1">
+    <row r="26" spans="1:11" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="8" t="s">
         <v>25</v>
       </c>
@@ -5246,13 +5246,13 @@
       </c>
       <c r="K26" s="17"/>
     </row>
-    <row r="27" spans="1:11" customFormat="1" ht="14.45">
+    <row r="27" spans="1:11" customFormat="1" ht="15" x14ac:dyDescent="0.25">
       <c r="K27" s="17"/>
     </row>
-    <row r="28" spans="1:11" customFormat="1" ht="14.45">
+    <row r="28" spans="1:11" customFormat="1" ht="15" x14ac:dyDescent="0.25">
       <c r="K28" s="17"/>
     </row>
-    <row r="29" spans="1:11" customFormat="1" ht="14.45">
+    <row r="29" spans="1:11" customFormat="1" ht="15" x14ac:dyDescent="0.25">
       <c r="A29" s="19" t="s">
         <v>27</v>
       </c>
@@ -5287,7 +5287,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="30" spans="1:11">
+    <row r="30" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A30" s="25" t="s">
         <v>38</v>
       </c>
@@ -5316,7 +5316,7 @@
       <c r="J30" s="26"/>
       <c r="K30" s="27"/>
     </row>
-    <row r="31" spans="1:11">
+    <row r="31" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A31" s="28"/>
       <c r="B31" s="29"/>
       <c r="C31" s="29"/>
@@ -5329,7 +5329,7 @@
       <c r="J31" s="29"/>
       <c r="K31" s="30"/>
     </row>
-    <row r="32" spans="1:11">
+    <row r="32" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A32" s="25"/>
       <c r="B32" s="26"/>
       <c r="C32" s="26"/>
@@ -5342,7 +5342,7 @@
       <c r="J32" s="26"/>
       <c r="K32" s="27"/>
     </row>
-    <row r="33" spans="1:11">
+    <row r="33" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A33" s="28"/>
       <c r="B33" s="29" t="s">
         <v>40</v>
@@ -5361,7 +5361,7 @@
       <c r="J33" s="29"/>
       <c r="K33" s="30"/>
     </row>
-    <row r="34" spans="1:11">
+    <row r="34" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A34" s="25"/>
       <c r="B34" s="26" t="s">
         <v>43</v>
@@ -5380,7 +5380,7 @@
       <c r="J34" s="26"/>
       <c r="K34" s="27"/>
     </row>
-    <row r="35" spans="1:11">
+    <row r="35" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A35" s="25"/>
       <c r="B35" s="26"/>
       <c r="C35" s="26"/>
@@ -5393,7 +5393,7 @@
       <c r="J35" s="26"/>
       <c r="K35" s="27"/>
     </row>
-    <row r="36" spans="1:11">
+    <row r="36" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A36" s="25"/>
       <c r="B36" s="26"/>
       <c r="C36" s="26"/>
@@ -5406,7 +5406,7 @@
       <c r="J36" s="26"/>
       <c r="K36" s="27"/>
     </row>
-    <row r="37" spans="1:11">
+    <row r="37" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A37" s="25"/>
       <c r="B37" s="26"/>
       <c r="C37" s="26"/>
@@ -5419,7 +5419,7 @@
       <c r="J37" s="26"/>
       <c r="K37" s="27"/>
     </row>
-    <row r="38" spans="1:11">
+    <row r="38" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A38" s="25"/>
       <c r="B38" s="26"/>
       <c r="C38" s="26"/>
@@ -5432,7 +5432,7 @@
       <c r="J38" s="26"/>
       <c r="K38" s="27"/>
     </row>
-    <row r="39" spans="1:11">
+    <row r="39" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A39" s="25"/>
       <c r="B39" s="26"/>
       <c r="C39" s="26"/>
@@ -5445,7 +5445,7 @@
       <c r="J39" s="26"/>
       <c r="K39" s="27"/>
     </row>
-    <row r="40" spans="1:11">
+    <row r="40" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A40" s="25"/>
       <c r="B40" s="26"/>
       <c r="C40" s="26"/>
@@ -5458,7 +5458,7 @@
       <c r="J40" s="26"/>
       <c r="K40" s="27"/>
     </row>
-    <row r="41" spans="1:11">
+    <row r="41" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A41" s="28"/>
       <c r="B41" s="29"/>
       <c r="C41" s="29"/>
@@ -5471,7 +5471,7 @@
       <c r="J41" s="29"/>
       <c r="K41" s="30"/>
     </row>
-    <row r="42" spans="1:11">
+    <row r="42" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A42" s="25"/>
       <c r="B42" s="26"/>
       <c r="C42" s="26"/>
@@ -5484,7 +5484,7 @@
       <c r="J42" s="26"/>
       <c r="K42" s="27"/>
     </row>
-    <row r="43" spans="1:11">
+    <row r="43" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A43" s="25"/>
       <c r="B43" s="26"/>
       <c r="C43" s="26"/>
@@ -5497,7 +5497,7 @@
       <c r="J43" s="26"/>
       <c r="K43" s="27"/>
     </row>
-    <row r="44" spans="1:11">
+    <row r="44" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A44" s="25"/>
       <c r="B44" s="26"/>
       <c r="C44" s="26"/>
@@ -5510,7 +5510,7 @@
       <c r="J44" s="26"/>
       <c r="K44" s="27"/>
     </row>
-    <row r="45" spans="1:11">
+    <row r="45" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A45" s="25"/>
       <c r="B45" s="26"/>
       <c r="C45" s="26"/>
@@ -5523,7 +5523,7 @@
       <c r="J45" s="26"/>
       <c r="K45" s="27"/>
     </row>
-    <row r="46" spans="1:11">
+    <row r="46" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A46" s="25"/>
       <c r="B46" s="26"/>
       <c r="C46" s="26"/>
@@ -5536,7 +5536,7 @@
       <c r="J46" s="26"/>
       <c r="K46" s="27"/>
     </row>
-    <row r="47" spans="1:11">
+    <row r="47" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A47" s="25"/>
       <c r="B47" s="26"/>
       <c r="C47" s="26"/>
@@ -5549,7 +5549,7 @@
       <c r="J47" s="26"/>
       <c r="K47" s="27"/>
     </row>
-    <row r="48" spans="1:11">
+    <row r="48" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A48" s="25"/>
       <c r="B48" s="26"/>
       <c r="C48" s="26"/>
@@ -5562,7 +5562,7 @@
       <c r="J48" s="26"/>
       <c r="K48" s="27"/>
     </row>
-    <row r="49" spans="1:11">
+    <row r="49" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A49" s="25"/>
       <c r="B49" s="26"/>
       <c r="C49" s="26"/>
@@ -5575,7 +5575,7 @@
       <c r="J49" s="26"/>
       <c r="K49" s="27"/>
     </row>
-    <row r="50" spans="1:11">
+    <row r="50" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A50" s="25"/>
       <c r="B50" s="26"/>
       <c r="C50" s="26"/>
@@ -5588,7 +5588,7 @@
       <c r="J50" s="26"/>
       <c r="K50" s="27"/>
     </row>
-    <row r="51" spans="1:11">
+    <row r="51" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A51" s="25"/>
       <c r="B51" s="26"/>
       <c r="C51" s="26"/>
@@ -5601,7 +5601,7 @@
       <c r="J51" s="26"/>
       <c r="K51" s="27"/>
     </row>
-    <row r="52" spans="1:11">
+    <row r="52" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A52" s="25"/>
       <c r="B52" s="26"/>
       <c r="C52" s="26"/>
@@ -5614,7 +5614,7 @@
       <c r="J52" s="26"/>
       <c r="K52" s="27"/>
     </row>
-    <row r="53" spans="1:11">
+    <row r="53" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A53" s="25"/>
       <c r="B53" s="26"/>
       <c r="C53" s="26"/>
@@ -5627,7 +5627,7 @@
       <c r="J53" s="26"/>
       <c r="K53" s="27"/>
     </row>
-    <row r="54" spans="1:11">
+    <row r="54" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A54" s="25"/>
       <c r="B54" s="26"/>
       <c r="C54" s="26"/>
@@ -5640,7 +5640,7 @@
       <c r="J54" s="26"/>
       <c r="K54" s="27"/>
     </row>
-    <row r="55" spans="1:11">
+    <row r="55" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A55" s="25"/>
       <c r="B55" s="26"/>
       <c r="C55" s="26"/>
@@ -5653,7 +5653,7 @@
       <c r="J55" s="26"/>
       <c r="K55" s="27"/>
     </row>
-    <row r="56" spans="1:11">
+    <row r="56" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A56" s="25"/>
       <c r="B56" s="26"/>
       <c r="C56" s="26"/>
@@ -5666,7 +5666,7 @@
       <c r="J56" s="26"/>
       <c r="K56" s="27"/>
     </row>
-    <row r="57" spans="1:11">
+    <row r="57" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A57" s="25"/>
       <c r="B57" s="26"/>
       <c r="C57" s="26"/>
@@ -5679,7 +5679,7 @@
       <c r="J57" s="26"/>
       <c r="K57" s="27"/>
     </row>
-    <row r="58" spans="1:11">
+    <row r="58" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A58" s="25"/>
       <c r="B58" s="26"/>
       <c r="C58" s="26"/>
@@ -5692,7 +5692,7 @@
       <c r="J58" s="26"/>
       <c r="K58" s="27"/>
     </row>
-    <row r="59" spans="1:11">
+    <row r="59" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A59" s="25"/>
       <c r="B59" s="26"/>
       <c r="C59" s="26"/>
@@ -5705,7 +5705,7 @@
       <c r="J59" s="26"/>
       <c r="K59" s="27"/>
     </row>
-    <row r="60" spans="1:11">
+    <row r="60" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A60" s="25"/>
       <c r="B60" s="26"/>
       <c r="C60" s="26"/>
@@ -5718,7 +5718,7 @@
       <c r="J60" s="26"/>
       <c r="K60" s="27"/>
     </row>
-    <row r="61" spans="1:11">
+    <row r="61" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A61" s="25"/>
       <c r="B61" s="26"/>
       <c r="C61" s="26"/>
@@ -5731,7 +5731,7 @@
       <c r="J61" s="26"/>
       <c r="K61" s="27"/>
     </row>
-    <row r="62" spans="1:11">
+    <row r="62" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A62" s="25"/>
       <c r="B62" s="26"/>
       <c r="C62" s="26"/>
@@ -5744,7 +5744,7 @@
       <c r="J62" s="26"/>
       <c r="K62" s="27"/>
     </row>
-    <row r="63" spans="1:11">
+    <row r="63" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A63" s="25"/>
       <c r="B63" s="26"/>
       <c r="C63" s="26"/>
@@ -5757,7 +5757,7 @@
       <c r="J63" s="26"/>
       <c r="K63" s="27"/>
     </row>
-    <row r="64" spans="1:11">
+    <row r="64" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A64" s="25"/>
       <c r="B64" s="26"/>
       <c r="C64" s="26"/>
@@ -5770,7 +5770,7 @@
       <c r="J64" s="26"/>
       <c r="K64" s="27"/>
     </row>
-    <row r="65" spans="1:11">
+    <row r="65" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A65" s="25"/>
       <c r="B65" s="26"/>
       <c r="C65" s="26"/>
@@ -5783,7 +5783,7 @@
       <c r="J65" s="26"/>
       <c r="K65" s="27"/>
     </row>
-    <row r="66" spans="1:11">
+    <row r="66" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A66" s="25"/>
       <c r="B66" s="26"/>
       <c r="C66" s="26"/>
@@ -5796,7 +5796,7 @@
       <c r="J66" s="26"/>
       <c r="K66" s="27"/>
     </row>
-    <row r="67" spans="1:11">
+    <row r="67" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A67" s="25"/>
       <c r="B67" s="26"/>
       <c r="C67" s="26"/>
@@ -5809,7 +5809,7 @@
       <c r="J67" s="26"/>
       <c r="K67" s="27"/>
     </row>
-    <row r="68" spans="1:11">
+    <row r="68" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A68" s="25"/>
       <c r="B68" s="26"/>
       <c r="C68" s="26"/>
@@ -5822,7 +5822,7 @@
       <c r="J68" s="26"/>
       <c r="K68" s="27"/>
     </row>
-    <row r="69" spans="1:11">
+    <row r="69" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A69" s="25"/>
       <c r="B69" s="26"/>
       <c r="C69" s="26"/>
@@ -5835,7 +5835,7 @@
       <c r="J69" s="26"/>
       <c r="K69" s="27"/>
     </row>
-    <row r="70" spans="1:11">
+    <row r="70" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A70" s="25"/>
       <c r="B70" s="26"/>
       <c r="C70" s="26"/>
@@ -5848,7 +5848,7 @@
       <c r="J70" s="26"/>
       <c r="K70" s="27"/>
     </row>
-    <row r="71" spans="1:11">
+    <row r="71" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A71" s="25"/>
       <c r="B71" s="26"/>
       <c r="C71" s="26"/>
@@ -5861,7 +5861,7 @@
       <c r="J71" s="26"/>
       <c r="K71" s="27"/>
     </row>
-    <row r="72" spans="1:11">
+    <row r="72" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A72" s="25"/>
       <c r="B72" s="26"/>
       <c r="C72" s="26"/>
@@ -5874,7 +5874,7 @@
       <c r="J72" s="26"/>
       <c r="K72" s="27"/>
     </row>
-    <row r="73" spans="1:11">
+    <row r="73" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A73" s="25"/>
       <c r="B73" s="26"/>
       <c r="C73" s="26"/>
@@ -5887,7 +5887,7 @@
       <c r="J73" s="26"/>
       <c r="K73" s="27"/>
     </row>
-    <row r="74" spans="1:11">
+    <row r="74" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A74" s="25"/>
       <c r="B74" s="26"/>
       <c r="C74" s="26"/>
@@ -5900,7 +5900,7 @@
       <c r="J74" s="26"/>
       <c r="K74" s="27"/>
     </row>
-    <row r="75" spans="1:11">
+    <row r="75" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A75" s="25"/>
       <c r="B75" s="26"/>
       <c r="C75" s="26"/>
@@ -5913,7 +5913,7 @@
       <c r="J75" s="26"/>
       <c r="K75" s="27"/>
     </row>
-    <row r="76" spans="1:11">
+    <row r="76" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A76" s="25"/>
       <c r="B76" s="26"/>
       <c r="C76" s="26"/>
@@ -5926,7 +5926,7 @@
       <c r="J76" s="26"/>
       <c r="K76" s="27"/>
     </row>
-    <row r="77" spans="1:11">
+    <row r="77" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A77" s="25"/>
       <c r="B77" s="26"/>
       <c r="C77" s="26"/>
@@ -5939,7 +5939,7 @@
       <c r="J77" s="26"/>
       <c r="K77" s="27"/>
     </row>
-    <row r="78" spans="1:11">
+    <row r="78" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A78" s="25"/>
       <c r="B78" s="26"/>
       <c r="C78" s="26"/>
@@ -5952,7 +5952,7 @@
       <c r="J78" s="26"/>
       <c r="K78" s="27"/>
     </row>
-    <row r="79" spans="1:11">
+    <row r="79" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A79" s="25"/>
       <c r="B79" s="26"/>
       <c r="C79" s="26"/>
@@ -5965,7 +5965,7 @@
       <c r="J79" s="26"/>
       <c r="K79" s="27"/>
     </row>
-    <row r="80" spans="1:11">
+    <row r="80" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A80" s="25"/>
       <c r="B80" s="26"/>
       <c r="C80" s="26"/>
@@ -5978,7 +5978,7 @@
       <c r="J80" s="26"/>
       <c r="K80" s="27"/>
     </row>
-    <row r="81" spans="1:11">
+    <row r="81" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A81" s="25"/>
       <c r="B81" s="26"/>
       <c r="C81" s="26"/>
@@ -5991,7 +5991,7 @@
       <c r="J81" s="26"/>
       <c r="K81" s="27"/>
     </row>
-    <row r="82" spans="1:11">
+    <row r="82" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A82" s="25"/>
       <c r="B82" s="26"/>
       <c r="C82" s="26"/>
@@ -6004,7 +6004,7 @@
       <c r="J82" s="26"/>
       <c r="K82" s="27"/>
     </row>
-    <row r="83" spans="1:11">
+    <row r="83" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A83" s="25"/>
       <c r="B83" s="26"/>
       <c r="C83" s="26"/>
@@ -6017,7 +6017,7 @@
       <c r="J83" s="26"/>
       <c r="K83" s="27"/>
     </row>
-    <row r="84" spans="1:11">
+    <row r="84" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A84" s="25"/>
       <c r="B84" s="26"/>
       <c r="C84" s="26"/>
@@ -6030,7 +6030,7 @@
       <c r="J84" s="26"/>
       <c r="K84" s="27"/>
     </row>
-    <row r="85" spans="1:11">
+    <row r="85" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A85" s="25"/>
       <c r="B85" s="26"/>
       <c r="C85" s="26"/>
@@ -6043,7 +6043,7 @@
       <c r="J85" s="26"/>
       <c r="K85" s="27"/>
     </row>
-    <row r="86" spans="1:11">
+    <row r="86" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A86" s="25"/>
       <c r="B86" s="26"/>
       <c r="C86" s="26"/>
@@ -6056,7 +6056,7 @@
       <c r="J86" s="26"/>
       <c r="K86" s="27"/>
     </row>
-    <row r="87" spans="1:11">
+    <row r="87" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A87" s="25"/>
       <c r="B87" s="26"/>
       <c r="C87" s="26"/>
@@ -6069,7 +6069,7 @@
       <c r="J87" s="26"/>
       <c r="K87" s="27"/>
     </row>
-    <row r="88" spans="1:11">
+    <row r="88" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A88" s="25"/>
       <c r="B88" s="26"/>
       <c r="C88" s="26"/>
@@ -6082,7 +6082,7 @@
       <c r="J88" s="26"/>
       <c r="K88" s="27"/>
     </row>
-    <row r="89" spans="1:11">
+    <row r="89" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A89" s="25"/>
       <c r="B89" s="26"/>
       <c r="C89" s="26"/>
@@ -6095,7 +6095,7 @@
       <c r="J89" s="26"/>
       <c r="K89" s="27"/>
     </row>
-    <row r="90" spans="1:11">
+    <row r="90" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A90" s="25"/>
       <c r="B90" s="26"/>
       <c r="C90" s="26"/>
@@ -6108,7 +6108,7 @@
       <c r="J90" s="26"/>
       <c r="K90" s="27"/>
     </row>
-    <row r="91" spans="1:11">
+    <row r="91" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A91" s="25"/>
       <c r="B91" s="26"/>
       <c r="C91" s="26"/>
@@ -6121,7 +6121,7 @@
       <c r="J91" s="26"/>
       <c r="K91" s="27"/>
     </row>
-    <row r="92" spans="1:11">
+    <row r="92" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A92" s="25"/>
       <c r="B92" s="26"/>
       <c r="C92" s="26"/>
@@ -6134,7 +6134,7 @@
       <c r="J92" s="26"/>
       <c r="K92" s="27"/>
     </row>
-    <row r="93" spans="1:11">
+    <row r="93" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A93" s="25"/>
       <c r="B93" s="26"/>
       <c r="C93" s="26"/>
@@ -6147,7 +6147,7 @@
       <c r="J93" s="26"/>
       <c r="K93" s="27"/>
     </row>
-    <row r="94" spans="1:11">
+    <row r="94" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A94" s="25"/>
       <c r="B94" s="26"/>
       <c r="C94" s="26"/>
@@ -6160,7 +6160,7 @@
       <c r="J94" s="26"/>
       <c r="K94" s="27"/>
     </row>
-    <row r="95" spans="1:11">
+    <row r="95" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A95" s="25"/>
       <c r="B95" s="26"/>
       <c r="C95" s="26"/>
@@ -6173,7 +6173,7 @@
       <c r="J95" s="26"/>
       <c r="K95" s="27"/>
     </row>
-    <row r="96" spans="1:11">
+    <row r="96" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A96" s="25"/>
       <c r="B96" s="26"/>
       <c r="C96" s="26"/>
@@ -6186,7 +6186,7 @@
       <c r="J96" s="26"/>
       <c r="K96" s="27"/>
     </row>
-    <row r="97" spans="1:11">
+    <row r="97" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A97" s="25"/>
       <c r="B97" s="26"/>
       <c r="C97" s="26"/>
@@ -6199,7 +6199,7 @@
       <c r="J97" s="26"/>
       <c r="K97" s="27"/>
     </row>
-    <row r="98" spans="1:11">
+    <row r="98" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A98" s="25"/>
       <c r="B98" s="26"/>
       <c r="C98" s="26"/>
@@ -6212,7 +6212,7 @@
       <c r="J98" s="26"/>
       <c r="K98" s="27"/>
     </row>
-    <row r="99" spans="1:11">
+    <row r="99" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A99" s="25"/>
       <c r="B99" s="26"/>
       <c r="C99" s="26"/>
@@ -6225,7 +6225,7 @@
       <c r="J99" s="26"/>
       <c r="K99" s="27"/>
     </row>
-    <row r="100" spans="1:11">
+    <row r="100" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A100" s="25"/>
       <c r="B100" s="26"/>
       <c r="C100" s="26"/>
@@ -6238,7 +6238,7 @@
       <c r="J100" s="26"/>
       <c r="K100" s="27"/>
     </row>
-    <row r="101" spans="1:11">
+    <row r="101" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A101" s="25"/>
       <c r="B101" s="26"/>
       <c r="C101" s="26"/>
@@ -6251,7 +6251,7 @@
       <c r="J101" s="26"/>
       <c r="K101" s="27"/>
     </row>
-    <row r="102" spans="1:11">
+    <row r="102" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A102" s="25"/>
       <c r="B102" s="26"/>
       <c r="C102" s="26"/>
@@ -6264,7 +6264,7 @@
       <c r="J102" s="26"/>
       <c r="K102" s="27"/>
     </row>
-    <row r="103" spans="1:11">
+    <row r="103" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A103" s="25"/>
       <c r="B103" s="26"/>
       <c r="C103" s="26"/>
@@ -6277,7 +6277,7 @@
       <c r="J103" s="26"/>
       <c r="K103" s="27"/>
     </row>
-    <row r="104" spans="1:11">
+    <row r="104" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A104" s="25"/>
       <c r="B104" s="26"/>
       <c r="C104" s="26"/>
@@ -6290,7 +6290,7 @@
       <c r="J104" s="26"/>
       <c r="K104" s="27"/>
     </row>
-    <row r="105" spans="1:11">
+    <row r="105" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A105" s="25"/>
       <c r="B105" s="26"/>
       <c r="C105" s="26"/>
@@ -6303,7 +6303,7 @@
       <c r="J105" s="26"/>
       <c r="K105" s="27"/>
     </row>
-    <row r="106" spans="1:11">
+    <row r="106" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A106" s="25"/>
       <c r="B106" s="26"/>
       <c r="C106" s="26"/>
@@ -6316,7 +6316,7 @@
       <c r="J106" s="26"/>
       <c r="K106" s="27"/>
     </row>
-    <row r="107" spans="1:11">
+    <row r="107" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A107" s="25"/>
       <c r="B107" s="26"/>
       <c r="C107" s="26"/>
@@ -6329,7 +6329,7 @@
       <c r="J107" s="26"/>
       <c r="K107" s="27"/>
     </row>
-    <row r="108" spans="1:11">
+    <row r="108" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A108" s="25"/>
       <c r="B108" s="26"/>
       <c r="C108" s="26"/>
@@ -6342,7 +6342,7 @@
       <c r="J108" s="26"/>
       <c r="K108" s="27"/>
     </row>
-    <row r="109" spans="1:11">
+    <row r="109" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A109" s="25"/>
       <c r="B109" s="26"/>
       <c r="C109" s="26"/>
@@ -6355,7 +6355,7 @@
       <c r="J109" s="26"/>
       <c r="K109" s="27"/>
     </row>
-    <row r="110" spans="1:11">
+    <row r="110" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A110" s="25"/>
       <c r="B110" s="26"/>
       <c r="C110" s="26"/>
@@ -6368,7 +6368,7 @@
       <c r="J110" s="26"/>
       <c r="K110" s="27"/>
     </row>
-    <row r="111" spans="1:11">
+    <row r="111" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A111" s="25"/>
       <c r="B111" s="26"/>
       <c r="C111" s="26"/>
@@ -6381,7 +6381,7 @@
       <c r="J111" s="26"/>
       <c r="K111" s="27"/>
     </row>
-    <row r="112" spans="1:11">
+    <row r="112" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A112" s="25"/>
       <c r="B112" s="26"/>
       <c r="C112" s="26"/>
@@ -6394,7 +6394,7 @@
       <c r="J112" s="26"/>
       <c r="K112" s="27"/>
     </row>
-    <row r="113" spans="1:11">
+    <row r="113" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A113" s="25"/>
       <c r="B113" s="26"/>
       <c r="C113" s="26"/>
@@ -6407,7 +6407,7 @@
       <c r="J113" s="26"/>
       <c r="K113" s="27"/>
     </row>
-    <row r="114" spans="1:11">
+    <row r="114" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A114" s="25"/>
       <c r="B114" s="26"/>
       <c r="C114" s="26"/>
@@ -6420,7 +6420,7 @@
       <c r="J114" s="26"/>
       <c r="K114" s="27"/>
     </row>
-    <row r="115" spans="1:11">
+    <row r="115" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A115" s="25"/>
       <c r="B115" s="26"/>
       <c r="C115" s="26"/>
@@ -6433,7 +6433,7 @@
       <c r="J115" s="26"/>
       <c r="K115" s="27"/>
     </row>
-    <row r="116" spans="1:11">
+    <row r="116" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A116" s="25"/>
       <c r="B116" s="26"/>
       <c r="C116" s="26"/>
@@ -6446,7 +6446,7 @@
       <c r="J116" s="26"/>
       <c r="K116" s="27"/>
     </row>
-    <row r="117" spans="1:11">
+    <row r="117" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A117" s="25"/>
       <c r="B117" s="26"/>
       <c r="C117" s="26"/>
@@ -6459,7 +6459,7 @@
       <c r="J117" s="26"/>
       <c r="K117" s="27"/>
     </row>
-    <row r="118" spans="1:11">
+    <row r="118" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A118" s="25"/>
       <c r="B118" s="26"/>
       <c r="C118" s="26"/>
@@ -6472,7 +6472,7 @@
       <c r="J118" s="26"/>
       <c r="K118" s="27"/>
     </row>
-    <row r="119" spans="1:11">
+    <row r="119" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A119" s="25"/>
       <c r="B119" s="26"/>
       <c r="C119" s="26"/>
@@ -6485,7 +6485,7 @@
       <c r="J119" s="26"/>
       <c r="K119" s="27"/>
     </row>
-    <row r="120" spans="1:11">
+    <row r="120" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A120" s="25"/>
       <c r="B120" s="26"/>
       <c r="C120" s="26"/>
@@ -6498,7 +6498,7 @@
       <c r="J120" s="26"/>
       <c r="K120" s="27"/>
     </row>
-    <row r="121" spans="1:11">
+    <row r="121" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A121" s="25"/>
       <c r="B121" s="26"/>
       <c r="C121" s="26"/>
@@ -6511,7 +6511,7 @@
       <c r="J121" s="26"/>
       <c r="K121" s="27"/>
     </row>
-    <row r="122" spans="1:11">
+    <row r="122" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A122" s="25"/>
       <c r="B122" s="26"/>
       <c r="C122" s="26"/>
@@ -6524,7 +6524,7 @@
       <c r="J122" s="26"/>
       <c r="K122" s="27"/>
     </row>
-    <row r="123" spans="1:11">
+    <row r="123" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A123" s="25"/>
       <c r="B123" s="26"/>
       <c r="C123" s="26"/>
@@ -6537,7 +6537,7 @@
       <c r="J123" s="26"/>
       <c r="K123" s="27"/>
     </row>
-    <row r="124" spans="1:11">
+    <row r="124" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A124" s="25"/>
       <c r="B124" s="26"/>
       <c r="C124" s="26"/>
@@ -6550,7 +6550,7 @@
       <c r="J124" s="26"/>
       <c r="K124" s="27"/>
     </row>
-    <row r="125" spans="1:11">
+    <row r="125" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A125" s="25"/>
       <c r="B125" s="26"/>
       <c r="C125" s="26"/>
@@ -6563,7 +6563,7 @@
       <c r="J125" s="26"/>
       <c r="K125" s="27"/>
     </row>
-    <row r="126" spans="1:11">
+    <row r="126" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A126" s="25"/>
       <c r="B126" s="26"/>
       <c r="C126" s="26"/>
@@ -6576,7 +6576,7 @@
       <c r="J126" s="26"/>
       <c r="K126" s="27"/>
     </row>
-    <row r="127" spans="1:11">
+    <row r="127" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A127" s="25"/>
       <c r="B127" s="26"/>
       <c r="C127" s="26"/>
@@ -6589,7 +6589,7 @@
       <c r="J127" s="26"/>
       <c r="K127" s="27"/>
     </row>
-    <row r="128" spans="1:11">
+    <row r="128" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A128" s="25"/>
       <c r="B128" s="26"/>
       <c r="C128" s="26"/>
@@ -6602,7 +6602,7 @@
       <c r="J128" s="26"/>
       <c r="K128" s="27"/>
     </row>
-    <row r="129" spans="1:11">
+    <row r="129" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A129" s="25"/>
       <c r="B129" s="26"/>
       <c r="C129" s="26"/>
@@ -6615,7 +6615,7 @@
       <c r="J129" s="26"/>
       <c r="K129" s="27"/>
     </row>
-    <row r="130" spans="1:11">
+    <row r="130" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A130" s="25"/>
       <c r="B130" s="26"/>
       <c r="C130" s="26"/>
@@ -6628,7 +6628,7 @@
       <c r="J130" s="26"/>
       <c r="K130" s="27"/>
     </row>
-    <row r="131" spans="1:11">
+    <row r="131" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A131" s="25"/>
       <c r="B131" s="26"/>
       <c r="C131" s="26"/>
@@ -6641,7 +6641,7 @@
       <c r="J131" s="26"/>
       <c r="K131" s="27"/>
     </row>
-    <row r="132" spans="1:11">
+    <row r="132" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A132" s="25"/>
       <c r="B132" s="26"/>
       <c r="C132" s="26"/>
@@ -6654,7 +6654,7 @@
       <c r="J132" s="26"/>
       <c r="K132" s="27"/>
     </row>
-    <row r="133" spans="1:11">
+    <row r="133" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A133" s="25"/>
       <c r="B133" s="26"/>
       <c r="C133" s="26"/>
@@ -6667,7 +6667,7 @@
       <c r="J133" s="26"/>
       <c r="K133" s="27"/>
     </row>
-    <row r="134" spans="1:11">
+    <row r="134" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A134" s="25"/>
       <c r="B134" s="26"/>
       <c r="C134" s="26"/>
@@ -6680,7 +6680,7 @@
       <c r="J134" s="26"/>
       <c r="K134" s="27"/>
     </row>
-    <row r="135" spans="1:11">
+    <row r="135" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A135" s="25"/>
       <c r="B135" s="26"/>
       <c r="C135" s="26"/>
@@ -6693,7 +6693,7 @@
       <c r="J135" s="26"/>
       <c r="K135" s="27"/>
     </row>
-    <row r="136" spans="1:11">
+    <row r="136" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A136" s="25"/>
       <c r="B136" s="26"/>
       <c r="C136" s="26"/>
@@ -6706,7 +6706,7 @@
       <c r="J136" s="26"/>
       <c r="K136" s="27"/>
     </row>
-    <row r="137" spans="1:11">
+    <row r="137" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A137" s="25"/>
       <c r="B137" s="26"/>
       <c r="C137" s="26"/>
@@ -6719,7 +6719,7 @@
       <c r="J137" s="26"/>
       <c r="K137" s="27"/>
     </row>
-    <row r="138" spans="1:11">
+    <row r="138" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A138" s="25"/>
       <c r="B138" s="26"/>
       <c r="C138" s="26"/>
@@ -6732,7 +6732,7 @@
       <c r="J138" s="26"/>
       <c r="K138" s="27"/>
     </row>
-    <row r="139" spans="1:11">
+    <row r="139" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A139" s="25"/>
       <c r="B139" s="26"/>
       <c r="C139" s="26"/>
@@ -6745,7 +6745,7 @@
       <c r="J139" s="26"/>
       <c r="K139" s="27"/>
     </row>
-    <row r="140" spans="1:11">
+    <row r="140" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A140" s="25"/>
       <c r="B140" s="26"/>
       <c r="C140" s="26"/>
@@ -6758,7 +6758,7 @@
       <c r="J140" s="26"/>
       <c r="K140" s="27"/>
     </row>
-    <row r="141" spans="1:11">
+    <row r="141" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A141" s="25"/>
       <c r="B141" s="26"/>
       <c r="C141" s="26"/>
@@ -6771,7 +6771,7 @@
       <c r="J141" s="26"/>
       <c r="K141" s="27"/>
     </row>
-    <row r="142" spans="1:11">
+    <row r="142" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A142" s="25"/>
       <c r="B142" s="26"/>
       <c r="C142" s="26"/>
@@ -6784,7 +6784,7 @@
       <c r="J142" s="26"/>
       <c r="K142" s="27"/>
     </row>
-    <row r="143" spans="1:11">
+    <row r="143" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A143" s="25"/>
       <c r="B143" s="26"/>
       <c r="C143" s="26"/>
@@ -6797,7 +6797,7 @@
       <c r="J143" s="26"/>
       <c r="K143" s="27"/>
     </row>
-    <row r="144" spans="1:11">
+    <row r="144" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A144" s="25"/>
       <c r="B144" s="26"/>
       <c r="C144" s="26"/>
@@ -6810,7 +6810,7 @@
       <c r="J144" s="26"/>
       <c r="K144" s="27"/>
     </row>
-    <row r="145" spans="1:11">
+    <row r="145" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A145" s="25"/>
       <c r="B145" s="26"/>
       <c r="C145" s="26"/>
@@ -6823,7 +6823,7 @@
       <c r="J145" s="26"/>
       <c r="K145" s="27"/>
     </row>
-    <row r="146" spans="1:11">
+    <row r="146" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A146" s="25"/>
       <c r="B146" s="26"/>
       <c r="C146" s="26"/>
@@ -6836,7 +6836,7 @@
       <c r="J146" s="26"/>
       <c r="K146" s="27"/>
     </row>
-    <row r="147" spans="1:11">
+    <row r="147" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A147" s="25"/>
       <c r="B147" s="26"/>
       <c r="C147" s="26"/>
@@ -6849,7 +6849,7 @@
       <c r="J147" s="26"/>
       <c r="K147" s="27"/>
     </row>
-    <row r="148" spans="1:11">
+    <row r="148" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A148" s="25"/>
       <c r="B148" s="26"/>
       <c r="C148" s="26"/>
@@ -6862,7 +6862,7 @@
       <c r="J148" s="26"/>
       <c r="K148" s="27"/>
     </row>
-    <row r="149" spans="1:11">
+    <row r="149" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A149" s="25"/>
       <c r="B149" s="26"/>
       <c r="C149" s="26"/>
@@ -6875,7 +6875,7 @@
       <c r="J149" s="26"/>
       <c r="K149" s="27"/>
     </row>
-    <row r="150" spans="1:11">
+    <row r="150" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A150" s="25"/>
       <c r="B150" s="26"/>
       <c r="C150" s="26"/>
@@ -6888,7 +6888,7 @@
       <c r="J150" s="26"/>
       <c r="K150" s="27"/>
     </row>
-    <row r="151" spans="1:11">
+    <row r="151" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A151" s="25"/>
       <c r="B151" s="26"/>
       <c r="C151" s="26"/>
@@ -6901,7 +6901,7 @@
       <c r="J151" s="26"/>
       <c r="K151" s="27"/>
     </row>
-    <row r="152" spans="1:11">
+    <row r="152" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A152" s="25"/>
       <c r="B152" s="26"/>
       <c r="C152" s="26"/>
@@ -6914,7 +6914,7 @@
       <c r="J152" s="26"/>
       <c r="K152" s="27"/>
     </row>
-    <row r="153" spans="1:11">
+    <row r="153" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A153" s="25"/>
       <c r="B153" s="26"/>
       <c r="C153" s="26"/>
@@ -6927,7 +6927,7 @@
       <c r="J153" s="26"/>
       <c r="K153" s="27"/>
     </row>
-    <row r="154" spans="1:11">
+    <row r="154" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A154" s="25"/>
       <c r="B154" s="26"/>
       <c r="C154" s="26"/>
@@ -6940,7 +6940,7 @@
       <c r="J154" s="26"/>
       <c r="K154" s="27"/>
     </row>
-    <row r="155" spans="1:11">
+    <row r="155" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A155" s="25"/>
       <c r="B155" s="26"/>
       <c r="C155" s="26"/>
@@ -6953,7 +6953,7 @@
       <c r="J155" s="26"/>
       <c r="K155" s="27"/>
     </row>
-    <row r="156" spans="1:11">
+    <row r="156" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A156" s="25"/>
       <c r="B156" s="26"/>
       <c r="C156" s="26"/>
@@ -6966,7 +6966,7 @@
       <c r="J156" s="26"/>
       <c r="K156" s="27"/>
     </row>
-    <row r="157" spans="1:11">
+    <row r="157" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A157" s="25"/>
       <c r="B157" s="26"/>
       <c r="C157" s="26"/>
@@ -6979,7 +6979,7 @@
       <c r="J157" s="26"/>
       <c r="K157" s="27"/>
     </row>
-    <row r="158" spans="1:11">
+    <row r="158" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A158" s="25"/>
       <c r="B158" s="26"/>
       <c r="C158" s="26"/>
@@ -6992,7 +6992,7 @@
       <c r="J158" s="26"/>
       <c r="K158" s="27"/>
     </row>
-    <row r="159" spans="1:11">
+    <row r="159" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A159" s="25"/>
       <c r="B159" s="26"/>
       <c r="C159" s="26"/>
@@ -7005,7 +7005,7 @@
       <c r="J159" s="26"/>
       <c r="K159" s="27"/>
     </row>
-    <row r="160" spans="1:11">
+    <row r="160" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A160" s="25"/>
       <c r="B160" s="26"/>
       <c r="C160" s="26"/>
@@ -7018,7 +7018,7 @@
       <c r="J160" s="26"/>
       <c r="K160" s="27"/>
     </row>
-    <row r="161" spans="1:11">
+    <row r="161" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A161" s="25"/>
       <c r="B161" s="26"/>
       <c r="C161" s="26"/>
@@ -7031,7 +7031,7 @@
       <c r="J161" s="26"/>
       <c r="K161" s="27"/>
     </row>
-    <row r="162" spans="1:11">
+    <row r="162" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A162" s="25"/>
       <c r="B162" s="26"/>
       <c r="C162" s="26"/>
@@ -7044,7 +7044,7 @@
       <c r="J162" s="26"/>
       <c r="K162" s="27"/>
     </row>
-    <row r="163" spans="1:11">
+    <row r="163" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A163" s="25"/>
       <c r="B163" s="26"/>
       <c r="C163" s="26"/>
@@ -7057,7 +7057,7 @@
       <c r="J163" s="26"/>
       <c r="K163" s="27"/>
     </row>
-    <row r="164" spans="1:11">
+    <row r="164" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A164" s="25"/>
       <c r="B164" s="26"/>
       <c r="C164" s="26"/>
@@ -7070,7 +7070,7 @@
       <c r="J164" s="26"/>
       <c r="K164" s="27"/>
     </row>
-    <row r="165" spans="1:11">
+    <row r="165" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A165" s="25"/>
       <c r="B165" s="26"/>
       <c r="C165" s="26"/>
@@ -7083,7 +7083,7 @@
       <c r="J165" s="26"/>
       <c r="K165" s="27"/>
     </row>
-    <row r="166" spans="1:11">
+    <row r="166" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A166" s="25"/>
       <c r="B166" s="26"/>
       <c r="C166" s="26"/>
@@ -7096,7 +7096,7 @@
       <c r="J166" s="26"/>
       <c r="K166" s="27"/>
     </row>
-    <row r="167" spans="1:11">
+    <row r="167" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A167" s="25"/>
       <c r="B167" s="26"/>
       <c r="C167" s="26"/>
@@ -7109,7 +7109,7 @@
       <c r="J167" s="26"/>
       <c r="K167" s="27"/>
     </row>
-    <row r="168" spans="1:11">
+    <row r="168" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A168" s="25"/>
       <c r="B168" s="26"/>
       <c r="C168" s="26"/>
@@ -7122,7 +7122,7 @@
       <c r="J168" s="26"/>
       <c r="K168" s="27"/>
     </row>
-    <row r="169" spans="1:11">
+    <row r="169" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A169" s="25"/>
       <c r="B169" s="26"/>
       <c r="C169" s="26"/>
@@ -7135,7 +7135,7 @@
       <c r="J169" s="26"/>
       <c r="K169" s="27"/>
     </row>
-    <row r="170" spans="1:11">
+    <row r="170" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A170" s="25"/>
       <c r="B170" s="26"/>
       <c r="C170" s="26"/>
@@ -7148,7 +7148,7 @@
       <c r="J170" s="26"/>
       <c r="K170" s="27"/>
     </row>
-    <row r="171" spans="1:11">
+    <row r="171" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A171" s="25"/>
       <c r="B171" s="26"/>
       <c r="C171" s="26"/>
@@ -7161,7 +7161,7 @@
       <c r="J171" s="26"/>
       <c r="K171" s="27"/>
     </row>
-    <row r="172" spans="1:11">
+    <row r="172" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A172" s="25"/>
       <c r="B172" s="26"/>
       <c r="C172" s="26"/>
@@ -7174,7 +7174,7 @@
       <c r="J172" s="26"/>
       <c r="K172" s="27"/>
     </row>
-    <row r="173" spans="1:11">
+    <row r="173" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A173" s="25"/>
       <c r="B173" s="26"/>
       <c r="C173" s="26"/>
@@ -7187,7 +7187,7 @@
       <c r="J173" s="26"/>
       <c r="K173" s="27"/>
     </row>
-    <row r="174" spans="1:11">
+    <row r="174" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A174" s="25"/>
       <c r="B174" s="26"/>
       <c r="C174" s="26"/>
@@ -7200,7 +7200,7 @@
       <c r="J174" s="26"/>
       <c r="K174" s="27"/>
     </row>
-    <row r="175" spans="1:11">
+    <row r="175" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A175" s="25"/>
       <c r="B175" s="26"/>
       <c r="C175" s="26"/>
@@ -7213,7 +7213,7 @@
       <c r="J175" s="26"/>
       <c r="K175" s="27"/>
     </row>
-    <row r="176" spans="1:11">
+    <row r="176" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A176" s="25"/>
       <c r="B176" s="26"/>
       <c r="C176" s="26"/>
@@ -7226,7 +7226,7 @@
       <c r="J176" s="26"/>
       <c r="K176" s="27"/>
     </row>
-    <row r="177" spans="1:11">
+    <row r="177" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A177" s="25"/>
       <c r="B177" s="26"/>
       <c r="C177" s="26"/>
@@ -7239,7 +7239,7 @@
       <c r="J177" s="26"/>
       <c r="K177" s="27"/>
     </row>
-    <row r="178" spans="1:11">
+    <row r="178" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A178" s="25"/>
       <c r="B178" s="26"/>
       <c r="C178" s="26"/>
@@ -7252,7 +7252,7 @@
       <c r="J178" s="26"/>
       <c r="K178" s="27"/>
     </row>
-    <row r="179" spans="1:11">
+    <row r="179" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A179" s="28"/>
       <c r="B179" s="29"/>
       <c r="C179" s="29"/>
@@ -7265,7 +7265,7 @@
       <c r="J179" s="29"/>
       <c r="K179" s="30"/>
     </row>
-    <row r="180" spans="1:11">
+    <row r="180" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A180" s="28"/>
       <c r="B180" s="29"/>
       <c r="C180" s="29"/>
@@ -7278,7 +7278,7 @@
       <c r="J180" s="29"/>
       <c r="K180" s="30"/>
     </row>
-    <row r="181" spans="1:11">
+    <row r="181" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A181" s="25"/>
       <c r="B181" s="26"/>
       <c r="C181" s="26"/>
@@ -7291,7 +7291,7 @@
       <c r="J181" s="26"/>
       <c r="K181" s="27"/>
     </row>
-    <row r="182" spans="1:11">
+    <row r="182" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A182" s="25"/>
       <c r="B182" s="26"/>
       <c r="C182" s="26"/>
@@ -7304,7 +7304,7 @@
       <c r="J182" s="26"/>
       <c r="K182" s="27"/>
     </row>
-    <row r="183" spans="1:11">
+    <row r="183" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A183" s="25"/>
       <c r="B183" s="26"/>
       <c r="C183" s="26"/>
@@ -7317,7 +7317,7 @@
       <c r="J183" s="26"/>
       <c r="K183" s="27"/>
     </row>
-    <row r="184" spans="1:11">
+    <row r="184" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A184" s="25"/>
       <c r="B184" s="26"/>
       <c r="C184" s="26"/>
@@ -7330,7 +7330,7 @@
       <c r="J184" s="26"/>
       <c r="K184" s="27"/>
     </row>
-    <row r="185" spans="1:11">
+    <row r="185" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A185" s="28"/>
       <c r="B185" s="29"/>
       <c r="C185" s="29"/>
@@ -7343,7 +7343,7 @@
       <c r="J185" s="29"/>
       <c r="K185" s="30"/>
     </row>
-    <row r="186" spans="1:11">
+    <row r="186" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A186" s="25"/>
       <c r="B186" s="26"/>
       <c r="C186" s="26"/>
@@ -7356,7 +7356,7 @@
       <c r="J186" s="26"/>
       <c r="K186" s="27"/>
     </row>
-    <row r="187" spans="1:11">
+    <row r="187" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A187" s="25"/>
       <c r="B187" s="26"/>
       <c r="C187" s="26"/>
@@ -7369,7 +7369,7 @@
       <c r="J187" s="26"/>
       <c r="K187" s="27"/>
     </row>
-    <row r="188" spans="1:11">
+    <row r="188" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A188" s="25"/>
       <c r="B188" s="26"/>
       <c r="C188" s="26"/>
@@ -7382,7 +7382,7 @@
       <c r="J188" s="26"/>
       <c r="K188" s="27"/>
     </row>
-    <row r="189" spans="1:11">
+    <row r="189" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A189" s="25"/>
       <c r="B189" s="26"/>
       <c r="C189" s="26"/>
@@ -7395,7 +7395,7 @@
       <c r="J189" s="26"/>
       <c r="K189" s="27"/>
     </row>
-    <row r="190" spans="1:11">
+    <row r="190" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A190" s="25"/>
       <c r="B190" s="26"/>
       <c r="C190" s="26"/>
@@ -7408,7 +7408,7 @@
       <c r="J190" s="26"/>
       <c r="K190" s="27"/>
     </row>
-    <row r="191" spans="1:11">
+    <row r="191" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A191" s="25"/>
       <c r="B191" s="26"/>
       <c r="C191" s="26"/>
@@ -7421,7 +7421,7 @@
       <c r="J191" s="26"/>
       <c r="K191" s="27"/>
     </row>
-    <row r="192" spans="1:11">
+    <row r="192" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A192" s="25"/>
       <c r="B192" s="26"/>
       <c r="C192" s="26"/>
@@ -7434,7 +7434,7 @@
       <c r="J192" s="26"/>
       <c r="K192" s="27"/>
     </row>
-    <row r="193" spans="1:11">
+    <row r="193" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A193" s="25"/>
       <c r="B193" s="26"/>
       <c r="C193" s="26"/>
@@ -7447,7 +7447,7 @@
       <c r="J193" s="26"/>
       <c r="K193" s="27"/>
     </row>
-    <row r="194" spans="1:11">
+    <row r="194" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A194" s="25"/>
       <c r="B194" s="26"/>
       <c r="C194" s="26"/>
@@ -7460,7 +7460,7 @@
       <c r="J194" s="26"/>
       <c r="K194" s="27"/>
     </row>
-    <row r="195" spans="1:11">
+    <row r="195" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A195" s="25"/>
       <c r="B195" s="26"/>
       <c r="C195" s="26"/>
@@ -7473,7 +7473,7 @@
       <c r="J195" s="26"/>
       <c r="K195" s="27"/>
     </row>
-    <row r="196" spans="1:11">
+    <row r="196" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A196" s="25"/>
       <c r="B196" s="26"/>
       <c r="C196" s="26"/>
@@ -7486,7 +7486,7 @@
       <c r="J196" s="26"/>
       <c r="K196" s="27"/>
     </row>
-    <row r="197" spans="1:11">
+    <row r="197" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A197" s="25"/>
       <c r="B197" s="26"/>
       <c r="C197" s="26"/>
@@ -7499,7 +7499,7 @@
       <c r="J197" s="26"/>
       <c r="K197" s="27"/>
     </row>
-    <row r="198" spans="1:11">
+    <row r="198" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A198" s="25"/>
       <c r="B198" s="26"/>
       <c r="C198" s="26"/>
@@ -7512,7 +7512,7 @@
       <c r="J198" s="26"/>
       <c r="K198" s="27"/>
     </row>
-    <row r="199" spans="1:11">
+    <row r="199" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A199" s="25"/>
       <c r="B199" s="26"/>
       <c r="C199" s="26"/>
@@ -7525,7 +7525,7 @@
       <c r="J199" s="26"/>
       <c r="K199" s="27"/>
     </row>
-    <row r="200" spans="1:11">
+    <row r="200" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A200" s="25"/>
       <c r="B200" s="26"/>
       <c r="C200" s="26"/>
@@ -7538,7 +7538,7 @@
       <c r="J200" s="26"/>
       <c r="K200" s="27"/>
     </row>
-    <row r="201" spans="1:11">
+    <row r="201" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A201" s="25"/>
       <c r="B201" s="26"/>
       <c r="C201" s="26"/>
@@ -7551,7 +7551,7 @@
       <c r="J201" s="26"/>
       <c r="K201" s="27"/>
     </row>
-    <row r="202" spans="1:11">
+    <row r="202" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A202" s="25"/>
       <c r="B202" s="26"/>
       <c r="C202" s="26"/>
@@ -7564,7 +7564,7 @@
       <c r="J202" s="26"/>
       <c r="K202" s="27"/>
     </row>
-    <row r="203" spans="1:11">
+    <row r="203" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A203" s="25"/>
       <c r="B203" s="26"/>
       <c r="C203" s="26"/>
@@ -7577,7 +7577,7 @@
       <c r="J203" s="26"/>
       <c r="K203" s="27"/>
     </row>
-    <row r="204" spans="1:11">
+    <row r="204" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A204" s="25"/>
       <c r="B204" s="26"/>
       <c r="C204" s="26"/>
@@ -7590,7 +7590,7 @@
       <c r="J204" s="26"/>
       <c r="K204" s="27"/>
     </row>
-    <row r="205" spans="1:11">
+    <row r="205" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A205" s="28"/>
       <c r="B205" s="29"/>
       <c r="C205" s="29"/>
@@ -7603,7 +7603,7 @@
       <c r="J205" s="29"/>
       <c r="K205" s="30"/>
     </row>
-    <row r="206" spans="1:11">
+    <row r="206" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A206" s="25"/>
       <c r="B206" s="26"/>
       <c r="C206" s="26"/>
@@ -7616,7 +7616,7 @@
       <c r="J206" s="26"/>
       <c r="K206" s="27"/>
     </row>
-    <row r="207" spans="1:11">
+    <row r="207" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A207" s="25"/>
       <c r="B207" s="26"/>
       <c r="C207" s="26"/>
@@ -7629,7 +7629,7 @@
       <c r="J207" s="26"/>
       <c r="K207" s="27"/>
     </row>
-    <row r="208" spans="1:11">
+    <row r="208" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A208" s="25"/>
       <c r="B208" s="26"/>
       <c r="C208" s="26"/>
@@ -7642,7 +7642,7 @@
       <c r="J208" s="26"/>
       <c r="K208" s="27"/>
     </row>
-    <row r="209" spans="1:11">
+    <row r="209" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A209" s="25"/>
       <c r="B209" s="26"/>
       <c r="C209" s="26"/>
@@ -7655,7 +7655,7 @@
       <c r="J209" s="26"/>
       <c r="K209" s="27"/>
     </row>
-    <row r="210" spans="1:11">
+    <row r="210" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A210" s="25"/>
       <c r="B210" s="26"/>
       <c r="C210" s="26"/>
@@ -7668,7 +7668,7 @@
       <c r="J210" s="26"/>
       <c r="K210" s="27"/>
     </row>
-    <row r="211" spans="1:11">
+    <row r="211" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A211" s="25"/>
       <c r="B211" s="26"/>
       <c r="C211" s="26"/>
@@ -7681,7 +7681,7 @@
       <c r="J211" s="26"/>
       <c r="K211" s="27"/>
     </row>
-    <row r="212" spans="1:11">
+    <row r="212" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A212" s="25"/>
       <c r="B212" s="26"/>
       <c r="C212" s="26"/>
@@ -7694,7 +7694,7 @@
       <c r="J212" s="26"/>
       <c r="K212" s="27"/>
     </row>
-    <row r="213" spans="1:11">
+    <row r="213" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A213" s="25"/>
       <c r="B213" s="26"/>
       <c r="C213" s="26"/>
@@ -7707,7 +7707,7 @@
       <c r="J213" s="26"/>
       <c r="K213" s="27"/>
     </row>
-    <row r="214" spans="1:11">
+    <row r="214" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A214" s="25"/>
       <c r="B214" s="26"/>
       <c r="C214" s="26"/>
@@ -7720,7 +7720,7 @@
       <c r="J214" s="26"/>
       <c r="K214" s="27"/>
     </row>
-    <row r="215" spans="1:11">
+    <row r="215" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A215" s="25"/>
       <c r="B215" s="26"/>
       <c r="C215" s="26"/>
@@ -7733,7 +7733,7 @@
       <c r="J215" s="26"/>
       <c r="K215" s="27"/>
     </row>
-    <row r="216" spans="1:11">
+    <row r="216" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A216" s="25"/>
       <c r="B216" s="26"/>
       <c r="C216" s="26"/>
@@ -7746,7 +7746,7 @@
       <c r="J216" s="26"/>
       <c r="K216" s="27"/>
     </row>
-    <row r="217" spans="1:11">
+    <row r="217" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A217" s="25"/>
       <c r="B217" s="26"/>
       <c r="C217" s="26"/>
@@ -7759,7 +7759,7 @@
       <c r="J217" s="26"/>
       <c r="K217" s="27"/>
     </row>
-    <row r="218" spans="1:11">
+    <row r="218" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A218" s="25"/>
       <c r="B218" s="26"/>
       <c r="C218" s="26"/>
@@ -7772,7 +7772,7 @@
       <c r="J218" s="26"/>
       <c r="K218" s="27"/>
     </row>
-    <row r="219" spans="1:11">
+    <row r="219" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A219" s="25"/>
       <c r="B219" s="26"/>
       <c r="C219" s="26"/>
@@ -7785,12 +7785,12 @@
       <c r="J219" s="26"/>
       <c r="K219" s="27"/>
     </row>
-    <row r="221" spans="1:11">
+    <row r="221" spans="1:11" x14ac:dyDescent="0.2">
       <c r="B221" s="16"/>
       <c r="E221" s="24"/>
       <c r="H221" s="24"/>
     </row>
-    <row r="224" spans="1:11">
+    <row r="224" spans="1:11" x14ac:dyDescent="0.2">
       <c r="B224" s="16"/>
       <c r="E224" s="24"/>
       <c r="H224" s="24"/>
@@ -7807,7 +7807,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E67D171A-755A-4FD2-A280-32551E90FBF0}">
   <dimension ref="A1:K22"/>
-  <sheetFormatPr defaultRowHeight="14.45"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="19.42578125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="19.42578125" customWidth="1"/>
@@ -7818,7 +7818,7 @@
     <col min="10" max="10" width="23.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B1" s="37" t="s">
         <v>45</v>
       </c>
@@ -7839,7 +7839,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="2" spans="1:11">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>50</v>
       </c>
@@ -7865,7 +7865,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="3" spans="1:11" ht="15" customHeight="1">
+    <row r="3" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>54</v>
       </c>
@@ -7882,7 +7882,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:11" ht="15" customHeight="1">
+    <row r="4" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>55</v>
       </c>
@@ -7899,7 +7899,7 @@
         <v>0.275117401248751</v>
       </c>
     </row>
-    <row r="5" spans="1:11" ht="15" customHeight="1">
+    <row r="5" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>56</v>
       </c>
@@ -7916,7 +7916,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:11" ht="15" customHeight="1">
+    <row r="6" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>57</v>
       </c>
@@ -7933,7 +7933,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:11" ht="15" customHeight="1">
+    <row r="7" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>58</v>
       </c>
@@ -7950,7 +7950,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:11" ht="15" customHeight="1">
+    <row r="8" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>59</v>
       </c>
@@ -7967,7 +7967,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:11" ht="15.75" customHeight="1">
+    <row r="9" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>60</v>
       </c>
@@ -7984,7 +7984,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:11" ht="15.75" customHeight="1">
+    <row r="10" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>61</v>
       </c>
@@ -8001,7 +8001,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:11" ht="15.75" customHeight="1">
+    <row r="11" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>62</v>
       </c>
@@ -8018,7 +8018,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:11" ht="14.25" customHeight="1">
+    <row r="12" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>63</v>
       </c>
@@ -8035,7 +8035,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:11" ht="14.25" customHeight="1">
+    <row r="13" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>64</v>
       </c>
@@ -8052,7 +8052,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:11" ht="15.75" customHeight="1">
+    <row r="14" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>65</v>
       </c>
@@ -8069,7 +8069,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:11" ht="15.75" customHeight="1">
+    <row r="15" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>66</v>
       </c>
@@ -8086,7 +8086,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:11" ht="15.75" customHeight="1">
+    <row r="16" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>67</v>
       </c>
@@ -8103,7 +8103,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:11" ht="14.25" customHeight="1">
+    <row r="17" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>39</v>
       </c>
@@ -8122,7 +8122,7 @@
       <c r="J17" s="11"/>
       <c r="K17" s="11"/>
     </row>
-    <row r="18" spans="1:11" ht="14.25" customHeight="1">
+    <row r="18" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>68</v>
       </c>
@@ -8141,7 +8141,7 @@
       <c r="J18" s="11"/>
       <c r="K18" s="11"/>
     </row>
-    <row r="19" spans="1:11" ht="14.25" customHeight="1">
+    <row r="19" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>69</v>
       </c>
@@ -8160,7 +8160,7 @@
       <c r="J19" s="11"/>
       <c r="K19" s="11"/>
     </row>
-    <row r="20" spans="1:11" ht="15" customHeight="1">
+    <row r="20" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>70</v>
       </c>
@@ -8179,7 +8179,7 @@
       <c r="J20" s="11"/>
       <c r="K20" s="12"/>
     </row>
-    <row r="21" spans="1:11" ht="14.25" customHeight="1">
+    <row r="21" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>71</v>
       </c>
@@ -8198,7 +8198,7 @@
       <c r="J21" s="12"/>
       <c r="K21" s="11"/>
     </row>
-    <row r="22" spans="1:11">
+    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B22" s="13">
         <f>SUM(B3:B21)</f>
         <v>0</v>
@@ -8219,7 +8219,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DB44651F-0888-43FD-B8BB-308FA554EC3A}">
   <dimension ref="A1:S26"/>
-  <sheetFormatPr defaultRowHeight="14.45"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="22.7109375" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="22.42578125" bestFit="1" customWidth="1"/>
@@ -8241,7 +8241,7 @@
     <col min="19" max="19" width="16.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19">
+    <row r="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>54</v>
       </c>
@@ -8300,7 +8300,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="2" spans="1:19">
+    <row r="2" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A2" s="9" t="s">
         <v>72</v>
       </c>
@@ -8341,7 +8341,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="3" spans="1:19">
+    <row r="3" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A3" s="9" t="s">
         <v>85</v>
       </c>
@@ -8364,7 +8364,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="4" spans="1:19">
+    <row r="4" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A4" s="9" t="s">
         <v>92</v>
       </c>
@@ -8384,7 +8384,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="5" spans="1:19">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A5" s="9" t="s">
         <v>97</v>
       </c>
@@ -8398,7 +8398,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="6" spans="1:19">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A6" s="9"/>
       <c r="J6" s="9">
         <v>9988</v>
@@ -8407,92 +8407,92 @@
         <v>101</v>
       </c>
     </row>
-    <row r="7" spans="1:19">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A7" s="9"/>
       <c r="J7" s="9">
         <v>333</v>
       </c>
     </row>
-    <row r="8" spans="1:19">
+    <row r="8" spans="1:19" x14ac:dyDescent="0.25">
       <c r="J8" s="9">
         <v>1109</v>
       </c>
     </row>
-    <row r="9" spans="1:19">
+    <row r="9" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A9" s="9"/>
       <c r="J9" s="9">
         <v>1288</v>
       </c>
     </row>
-    <row r="10" spans="1:19">
+    <row r="10" spans="1:19" x14ac:dyDescent="0.25">
       <c r="J10" s="9">
         <v>2318</v>
       </c>
     </row>
-    <row r="11" spans="1:19">
+    <row r="11" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A11" s="9"/>
       <c r="J11" s="9">
         <v>2823</v>
       </c>
     </row>
-    <row r="12" spans="1:19">
+    <row r="12" spans="1:19" x14ac:dyDescent="0.25">
       <c r="J12" s="9">
         <v>2828</v>
       </c>
     </row>
-    <row r="13" spans="1:19">
+    <row r="13" spans="1:19" x14ac:dyDescent="0.25">
       <c r="J13" s="9">
         <v>883</v>
       </c>
     </row>
-    <row r="14" spans="1:19">
+    <row r="14" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A14" s="9"/>
       <c r="J14" s="9">
         <v>857</v>
       </c>
     </row>
-    <row r="15" spans="1:19">
+    <row r="15" spans="1:19" x14ac:dyDescent="0.25">
       <c r="J15" s="9">
         <v>600690</v>
       </c>
     </row>
-    <row r="16" spans="1:19">
+    <row r="16" spans="1:19" x14ac:dyDescent="0.25">
       <c r="J16" s="9">
         <v>688</v>
       </c>
     </row>
-    <row r="17" spans="1:18">
+    <row r="17" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A17" s="9"/>
       <c r="J17" s="9">
         <v>700</v>
       </c>
     </row>
-    <row r="18" spans="1:18">
+    <row r="18" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A18" s="9"/>
     </row>
-    <row r="20" spans="1:18">
+    <row r="20" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A20" s="9"/>
     </row>
-    <row r="22" spans="1:18">
+    <row r="22" spans="1:18" x14ac:dyDescent="0.25">
       <c r="O22" s="9"/>
       <c r="Q22" s="9"/>
       <c r="R22" s="9"/>
     </row>
-    <row r="23" spans="1:18">
+    <row r="23" spans="1:18" x14ac:dyDescent="0.25">
       <c r="O23" s="9"/>
       <c r="Q23" s="9"/>
       <c r="R23" s="9"/>
     </row>
-    <row r="24" spans="1:18">
+    <row r="24" spans="1:18" x14ac:dyDescent="0.25">
       <c r="O24" s="9"/>
       <c r="Q24" s="9"/>
       <c r="R24" s="9"/>
     </row>
-    <row r="25" spans="1:18">
+    <row r="25" spans="1:18" x14ac:dyDescent="0.25">
       <c r="O25" s="9"/>
       <c r="R25" s="9"/>
     </row>
-    <row r="26" spans="1:18">
+    <row r="26" spans="1:18" x14ac:dyDescent="0.25">
       <c r="O26" s="9"/>
     </row>
   </sheetData>
